--- a/backtest_runs/20260410_193658/by_symbol/POWERPS/POWERPS.xlsx
+++ b/backtest_runs/20260410_193658/by_symbol/POWERPS/POWERPS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0</v>
